--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260611.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260611.xlsx
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>24,777,339</t>
+          <t>62,908,735</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>62,908,735</t>
+          <t>24,777,339</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>144,035,940</t>
+          <t>37,386,029</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>37,386,029</t>
+          <t>144,035,940</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
